--- a/02_Zero_Shot/outputs/Embedding/ALBERT-base-v2/RESULT_f-droid_albert-base-v2_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/Embedding/ALBERT-base-v2/RESULT_f-droid_albert-base-v2_zeroshot.xlsx
@@ -48836,7 +48836,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.517110137000145</v>
+        <v>28.48111584299841</v>
       </c>
     </row>
     <row r="8">
@@ -48846,7 +48846,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002997926834565345</v>
+        <v>0.01002503197571222</v>
       </c>
     </row>
   </sheetData>
